--- a/input/ved_correct/ved_3031703_3 (6).xlsx
+++ b/input/ved_correct/ved_3031703_3 (6).xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -6787,37 +6787,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546a"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="e7e6e6"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5b9bd5"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ed7d31"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a5a5a5"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="ffc000"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472c4"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70ad47"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563c1"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954f72"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -6959,7 +6959,7 @@
   <dimension ref="A1:P465"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="23.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="23.77"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="20.43"/>
   </cols>
   <sheetData>
@@ -19837,7 +19837,7 @@
       <c r="C259" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="D259" s="0" t="s">
+      <c r="D259" s="1" t="s">
         <v>46</v>
       </c>
       <c r="E259" s="1" t="s">
